--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484859_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484859_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>F. MARCO CLIMENT</t>
+          <t>P. LUENGO MATEO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.603</v>
+        <v>5.9173</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3934</v>
+        <v>6.7728</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2096</v>
+        <v>-0.8554</v>
       </c>
       <c r="G2" t="n">
-        <v>4.231</v>
+        <v>4.3195</v>
       </c>
       <c r="H2" t="n">
-        <v>4.7331</v>
+        <v>4.2182</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5021</v>
+        <v>0.1013</v>
       </c>
       <c r="J2" t="n">
-        <v>4.7997</v>
+        <v>6.7134</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7175</v>
+        <v>4.9022</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0823</v>
+        <v>1.8112</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5687</v>
+        <v>-2.3939</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0157</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5843</v>
+        <v>-1.7099</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.7548</v>
+        <v>0.3774</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1322</v>
+        <v>1.3209</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1268</v>
+        <v>0.5979</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4807</v>
+        <v>0.3803</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6461</v>
+        <v>0.2176</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.6226</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>0.6226</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. LUENGO MATEO</t>
+          <t>F. MARCO CLIMENT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0056</v>
+        <v>5.1776</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9933</v>
+        <v>4.1268</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9877</v>
+        <v>1.0509</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3195</v>
+        <v>4.231</v>
       </c>
       <c r="H3" t="n">
-        <v>4.2182</v>
+        <v>4.7331</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1013</v>
+        <v>-0.5021</v>
       </c>
       <c r="J3" t="n">
-        <v>6.7134</v>
+        <v>4.7997</v>
       </c>
       <c r="K3" t="n">
-        <v>4.9022</v>
+        <v>4.7175</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8112</v>
+        <v>0.0823</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.3939</v>
+        <v>-0.5687</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6840000000000001</v>
+        <v>0.0157</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.7099</v>
+        <v>-0.5843</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3774</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3209</v>
+        <v>1.1322</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3139</v>
+        <v>1.7014</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3992</v>
+        <v>1.214</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0853</v>
+        <v>0.4874</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6226</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6226</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5558</v>
+        <v>5.0224</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3216</v>
+        <v>4.8676</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2342</v>
+        <v>0.1549</v>
       </c>
       <c r="G4" t="n">
         <v>3.9687</v>
@@ -766,13 +766,13 @@
         <v>1.5096</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1722</v>
+        <v>1.6388</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4267</v>
+        <v>0.9727</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7454</v>
+        <v>0.6661</v>
       </c>
       <c r="V4" t="n">
         <v>-0.019</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.1207</v>
+        <v>3.7851</v>
       </c>
       <c r="E5" t="n">
-        <v>3.7661</v>
+        <v>3.6687</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3545</v>
+        <v>0.1164</v>
       </c>
       <c r="G5" t="n">
         <v>2.8924</v>
@@ -844,13 +844,13 @@
         <v>1.6983</v>
       </c>
       <c r="S5" t="n">
-        <v>1.7377</v>
+        <v>1.4022</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8875999999999999</v>
+        <v>0.7902</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8501</v>
+        <v>0.612</v>
       </c>
       <c r="V5" t="n">
         <v>-0.3208</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. MARTINEZ JURADO</t>
+          <t>G. FONT FENOLLAR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1651</v>
+        <v>2.2349</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4951</v>
+        <v>1.3547</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.33</v>
+        <v>0.8802</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8507</v>
+        <v>1.2525</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7795</v>
+        <v>1.1442</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0712</v>
+        <v>0.1083</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3442</v>
+        <v>1.0142</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2208</v>
+        <v>1.0142</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1234</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1949</v>
+        <v>0.2383</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.0003</v>
+        <v>0.1299</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1946</v>
+        <v>0.1083</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1887</v>
+        <v>0.5661</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1322</v>
+        <v>0.5661</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5819</v>
+        <v>0.1145</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4907</v>
+        <v>0.0386</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0912</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2452</v>
+        <v>0.3018</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6036</v>
+        <v>0.3018</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6415999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. FONT FENOLLAR</t>
+          <t>A. LOPEZ ALVAREZ-TIRADOR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.0846</v>
+        <v>1.5881</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2573</v>
+        <v>1.1476</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8273</v>
+        <v>0.4405</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2525</v>
+        <v>-0.7456</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1442</v>
+        <v>-1.0596</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1083</v>
+        <v>0.314</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0142</v>
+        <v>0.7393999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0142</v>
+        <v>0.5337</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.2057</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2383</v>
+        <v>-1.485</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1299</v>
+        <v>-1.5934</v>
       </c>
       <c r="O8" t="n">
         <v>0.1083</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5661</v>
+        <v>0.9435</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5661</v>
+        <v>0.9435</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0359</v>
+        <v>0.7486</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0588</v>
+        <v>0.4082</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0229</v>
+        <v>0.3404</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3018</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. FAYE</t>
+          <t>D. MARTINEZ JURADO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0602</v>
+        <v>1.4973</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2931</v>
+        <v>1.7744</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2329</v>
+        <v>-0.277</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5227</v>
+        <v>-0.8507</v>
       </c>
       <c r="H9" t="n">
-        <v>0.263</v>
+        <v>-0.7795</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.7856</v>
+        <v>-0.0712</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6971000000000001</v>
+        <v>1.3442</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4915</v>
+        <v>1.2208</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2057</v>
+        <v>0.1234</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.2198</v>
+        <v>-2.1949</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2285</v>
+        <v>-2.0003</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.9913</v>
+        <v>-0.1946</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5096</v>
+        <v>0.1887</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6983</v>
+        <v>1.1322</v>
       </c>
       <c r="S9" t="n">
-        <v>2.3185</v>
+        <v>0.9141</v>
       </c>
       <c r="T9" t="n">
-        <v>1.7847</v>
+        <v>0.77</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5338000000000001</v>
+        <v>0.1441</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2452</v>
+        <v>1.2452</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2452</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. LOPEZ ALVAREZ-TIRADOR</t>
+          <t>P. FAYE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8389</v>
+        <v>0.8027</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5042</v>
+        <v>1.9033</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3346</v>
+        <v>-1.1006</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7456</v>
+        <v>-1.5227</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0596</v>
+        <v>0.263</v>
       </c>
       <c r="I10" t="n">
-        <v>0.314</v>
+        <v>-1.7856</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7393999999999999</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5337</v>
+        <v>0.4915</v>
       </c>
       <c r="L10" t="n">
         <v>0.2057</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.485</v>
+        <v>-2.2198</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5934</v>
+        <v>-0.2285</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1083</v>
+        <v>-1.9913</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9435</v>
+        <v>1.5096</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.1887</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9435</v>
+        <v>1.6983</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>2.061</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2352</v>
+        <v>1.3949</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2346</v>
+        <v>0.6661</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6415999999999999</v>
+        <v>-1.2452</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6415999999999999</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. CERVANTES GUERRA</t>
+          <t>P. ANTICH MINGUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2962</v>
+        <v>0.5741000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>2.1264</v>
+        <v>2.2477</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8302</v>
+        <v>-1.6736</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3797</v>
+        <v>-0.6942</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9751</v>
+        <v>2.2672</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5954</v>
+        <v>-2.9614</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9212</v>
+        <v>2.4738</v>
       </c>
       <c r="K11" t="n">
-        <v>3.3651</v>
+        <v>3.0325</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.4439</v>
+        <v>-0.5588</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.5415</v>
+        <v>-3.1679</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.39</v>
+        <v>-0.7654</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1515</v>
+        <v>-2.4026</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.2644</v>
+        <v>0.1887</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.8305</v>
+        <v>-1.1322</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5661</v>
+        <v>1.3209</v>
       </c>
       <c r="S11" t="n">
-        <v>2.5207</v>
+        <v>1.0796</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3754</v>
+        <v>0.9061</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1452</v>
+        <v>0.1735</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3398</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3398</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. ANTICH MINGUEZ</t>
+          <t>V. SANTAMATILDE PERIS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4338</v>
+        <v>-0.4775</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6631</v>
+        <v>0.6909</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0968</v>
+        <v>-1.1684</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6942</v>
+        <v>1.2566</v>
       </c>
       <c r="H12" t="n">
-        <v>2.2672</v>
+        <v>2.6655</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.9614</v>
+        <v>-1.4089</v>
       </c>
       <c r="J12" t="n">
-        <v>2.4738</v>
+        <v>2.5611</v>
       </c>
       <c r="K12" t="n">
-        <v>3.0325</v>
+        <v>2.5199</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5588</v>
+        <v>0.0411</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.1679</v>
+        <v>-1.3045</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7654</v>
+        <v>0.1456</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.4026</v>
+        <v>-1.4501</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1887</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1322</v>
+        <v>-2.0757</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3209</v>
+        <v>1.1322</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0717</v>
+        <v>0.7564</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3215</v>
+        <v>0.2056</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2498</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V. SANTAMATILDE PERIS</t>
+          <t>O. CASTRILLON RODRIGUEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.8589</v>
+        <v>-0.5586</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2038</v>
+        <v>-0.0355</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0626</v>
+        <v>-0.5231</v>
       </c>
       <c r="G13" t="n">
-        <v>1.2566</v>
+        <v>-2.7928</v>
       </c>
       <c r="H13" t="n">
-        <v>2.6655</v>
+        <v>-0.6887</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.4089</v>
+        <v>-2.1042</v>
       </c>
       <c r="J13" t="n">
-        <v>2.5611</v>
+        <v>-0.572</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5199</v>
+        <v>0.6448</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0411</v>
+        <v>-1.2169</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.3045</v>
+        <v>-2.2208</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1456</v>
+        <v>-1.3335</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.4501</v>
+        <v>-0.8873</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9435</v>
+        <v>0.9435</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.0757</v>
+        <v>-0.1887</v>
       </c>
       <c r="R13" t="n">
         <v>1.1322</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3751</v>
+        <v>1.2908</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2816</v>
+        <v>0.7252</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6567</v>
+        <v>0.5656</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.547</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>O. CASTRILLON RODRIGUEZ</t>
+          <t>L. CERVANTES GUERRA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.2562</v>
+        <v>-1.0884</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.9712</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.285</v>
+        <v>-1.9095</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.7928</v>
+        <v>0.3797</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.6887</v>
+        <v>0.9751</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.1042</v>
+        <v>-0.5954</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.572</v>
+        <v>2.9212</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6448</v>
+        <v>3.3651</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.2169</v>
+        <v>-0.4439</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.2208</v>
+        <v>-2.5415</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.3335</v>
+        <v>-2.39</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8873</v>
+        <v>-0.1515</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9435</v>
+        <v>-2.2644</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1887</v>
+        <v>-2.8305</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1322</v>
+        <v>0.5661</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5931999999999999</v>
+        <v>1.136</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2105</v>
+        <v>1.0701</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8037</v>
+        <v>0.0659</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-0.3398</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>-0.3398</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>27.2829</v>
+        <v>27.57670000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>32.1479</v>
+        <v>32.4418</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.865</v>
+        <v>-4.8647</v>
       </c>
       <c r="G15" t="n">
         <v>14.7961</v>
@@ -1600,7 +1600,7 @@
         <v>36.86969999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>31.46</v>
+        <v>31.45999999999999</v>
       </c>
       <c r="L15" t="n">
         <v>5.4096</v>
@@ -1615,7 +1615,7 @@
         <v>-10.9296</v>
       </c>
       <c r="P15" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>-14.1525</v>
@@ -1624,13 +1624,13 @@
         <v>14.1525</v>
       </c>
       <c r="S15" t="n">
-        <v>13.1474</v>
+        <v>13.4413</v>
       </c>
       <c r="T15" t="n">
-        <v>8.582000000000003</v>
+        <v>8.875900000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>4.5652</v>
+        <v>4.5654</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6606</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. STANESCU</t>
+          <t>S. VAL GUTIERREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6654</v>
+        <v>1.6832</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9957</v>
+        <v>6.8631</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6697</v>
+        <v>-5.1798</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1867</v>
+        <v>4.94</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.504</v>
+        <v>-3.1672</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6907</v>
+        <v>8.107100000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4637</v>
+        <v>11.2143</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4226</v>
+        <v>2.1983</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0411</v>
+        <v>9.016</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.277</v>
+        <v>-6.2743</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9266</v>
+        <v>-5.3654</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6496</v>
+        <v>-0.9089</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5661</v>
+        <v>-2.8305</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-4.7175</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5661</v>
+        <v>1.887</v>
       </c>
       <c r="S16" t="n">
-        <v>0.271</v>
+        <v>-1.9922</v>
       </c>
       <c r="T16" t="n">
-        <v>0.532</v>
+        <v>-0.8789</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.261</v>
+        <v>-1.1133</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6415999999999999</v>
+        <v>1.566</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. VAL GUTIERREZ</t>
+          <t>R. STANESCU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3417</v>
+        <v>1.4501</v>
       </c>
       <c r="E17" t="n">
-        <v>6.8631</v>
+        <v>0.7034</v>
       </c>
       <c r="F17" t="n">
-        <v>-5.5214</v>
+        <v>0.7467</v>
       </c>
       <c r="G17" t="n">
-        <v>4.94</v>
+        <v>0.1867</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.1672</v>
+        <v>-0.504</v>
       </c>
       <c r="I17" t="n">
-        <v>8.107100000000001</v>
+        <v>0.6907</v>
       </c>
       <c r="J17" t="n">
-        <v>11.2143</v>
+        <v>0.4637</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1983</v>
+        <v>0.4226</v>
       </c>
       <c r="L17" t="n">
-        <v>9.016</v>
+        <v>0.0411</v>
       </c>
       <c r="M17" t="n">
-        <v>-6.2743</v>
+        <v>-0.277</v>
       </c>
       <c r="N17" t="n">
-        <v>-5.3654</v>
+        <v>-0.9266</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9089</v>
+        <v>0.6496</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.8305</v>
+        <v>0.5661</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.7175</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.887</v>
+        <v>0.5661</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.3338</v>
+        <v>0.0557</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8789</v>
+        <v>0.2397</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.4549</v>
+        <v>-0.184</v>
       </c>
       <c r="V17" t="n">
-        <v>1.566</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3208</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9599</v>
+        <v>0.9863</v>
       </c>
       <c r="E19" t="n">
         <v>1.0688</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.109</v>
+        <v>-0.0825</v>
       </c>
       <c r="G19" t="n">
         <v>-0.3741</v>
@@ -1936,13 +1936,13 @@
         <v>0.3774</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2886</v>
+        <v>-0.2622</v>
       </c>
       <c r="T19" t="n">
         <v>-0.1764</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1123</v>
+        <v>-0.0858</v>
       </c>
       <c r="V19" t="n">
         <v>1.2452</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. DE ANDREA LUNA</t>
+          <t>J. SANABRIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3169</v>
+        <v>-1.4473</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3956</v>
+        <v>0.4804</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.7125</v>
+        <v>-1.9277</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2461</v>
+        <v>-1.1569</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0094</v>
+        <v>-0.3623</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2555</v>
+        <v>-0.7945</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0988</v>
+        <v>1.4763</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0988</v>
+        <v>2.0762</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0.5999</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.3448</v>
+        <v>-2.6332</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0894</v>
+        <v>-2.4386</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2555</v>
+        <v>-0.1946</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3774</v>
+        <v>1.1322</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3774</v>
+        <v>1.1322</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1464</v>
+        <v>-0.7811</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2968</v>
+        <v>-0.3544</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4432</v>
+        <v>-0.4267</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3018</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. SANABRIA</t>
+          <t>I. DE ANDREA LUNA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8696</v>
+        <v>-1.6802</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1881</v>
+        <v>1.0059</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0576</v>
+        <v>-2.686</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.1569</v>
+        <v>-1.2461</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3623</v>
+        <v>0.0094</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7945</v>
+        <v>-1.2555</v>
       </c>
       <c r="J21" t="n">
-        <v>1.4763</v>
+        <v>1.0988</v>
       </c>
       <c r="K21" t="n">
-        <v>2.0762</v>
+        <v>1.0988</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5999</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.6332</v>
+        <v>-2.3448</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.4386</v>
+        <v>-1.0894</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1946</v>
+        <v>-1.2555</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1322</v>
+        <v>0.3774</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1322</v>
+        <v>0.3774</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2033</v>
+        <v>-0.5097</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.0929</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5567</v>
+        <v>-0.4168</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-0.3018</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3837</v>
+        <v>-1.8412</v>
       </c>
       <c r="E22" t="n">
-        <v>2.7721</v>
+        <v>2.8696</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.1558</v>
+        <v>-4.7108</v>
       </c>
       <c r="G22" t="n">
         <v>0.9258</v>
@@ -2170,13 +2170,13 @@
         <v>2.0757</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.2338</v>
+        <v>-1.6914</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7026</v>
+        <v>-0.6051</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.5313</v>
+        <v>-1.0863</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3208</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8207</v>
+        <v>-3.5464</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3662</v>
+        <v>-1.1713</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4545</v>
+        <v>-2.3751</v>
       </c>
       <c r="G23" t="n">
         <v>-2.8836</v>
@@ -2248,13 +2248,13 @@
         <v>0.9435</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9370000000000001</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5291</v>
+        <v>-0.3342</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.408</v>
+        <v>-0.3286</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.1881</v>
+        <v>-5.7858</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.2318</v>
+        <v>-1.7189</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.9563</v>
+        <v>-4.0669</v>
       </c>
       <c r="G24" t="n">
         <v>-4.0364</v>
@@ -2326,13 +2326,13 @@
         <v>1.887</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.85</v>
+        <v>-1.4477</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0058</v>
+        <v>-0.4814</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8558</v>
+        <v>-0.9664</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2452</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.6524</v>
+        <v>-7.7605</v>
       </c>
       <c r="E25" t="n">
         <v>-2.4246</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.2277</v>
+        <v>-5.3359</v>
       </c>
       <c r="G25" t="n">
         <v>-5.8652</v>
@@ -2404,13 +2404,13 @@
         <v>2.0757</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.693</v>
+        <v>-1.8012</v>
       </c>
       <c r="T25" t="n">
         <v>-0.7613</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.9317</v>
+        <v>-1.0398</v>
       </c>
       <c r="V25" t="n">
         <v>-0.2828</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-10.2865</v>
+        <v>-9.309799999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.6638</v>
+        <v>-4.0792</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.6227</v>
+        <v>-5.2306</v>
       </c>
       <c r="G26" t="n">
         <v>-6.5542</v>
@@ -2482,13 +2482,13 @@
         <v>2.8305</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.7323</v>
+        <v>-2.7556</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.7048</v>
+        <v>-1.1202</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.0274</v>
+        <v>-1.6353</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-27.2831</v>
+        <v>-25.9838</v>
       </c>
       <c r="E27" t="n">
-        <v>4.864799999999999</v>
+        <v>4.865</v>
       </c>
       <c r="F27" t="n">
-        <v>-32.1478</v>
+        <v>-30.8486</v>
       </c>
       <c r="G27" t="n">
         <v>-14.7962</v>
@@ -2560,13 +2560,13 @@
         <v>14.1525</v>
       </c>
       <c r="S27" t="n">
-        <v>-13.1472</v>
+        <v>-11.8482</v>
       </c>
       <c r="T27" t="n">
-        <v>-4.565200000000001</v>
+        <v>-4.565099999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>-8.5823</v>
+        <v>-7.283</v>
       </c>
       <c r="V27" t="n">
         <v>0.6606000000000001</v>
